--- a/src/__tests__/thirdParties/web/__testFiles__/Modifica Dep Mal 2.xlsx
+++ b/src/__tests__/thirdParties/web/__testFiles__/Modifica Dep Mal 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Proyectos\cali-mobility\cali-mobility-backend\src\__tests__\thirdParties\web\__testFiles__\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1594E68-32F0-48F1-88B0-C9F035529101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D64D301-76A8-49DD-A241-3A58705E2365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,13 +39,13 @@
     <t>TEST</t>
   </si>
   <si>
-    <t>TEST 1</t>
-  </si>
-  <si>
-    <t>TEST 2</t>
-  </si>
-  <si>
-    <t>TEST 3</t>
+    <t>TEST 10</t>
+  </si>
+  <si>
+    <t>TEST 11</t>
+  </si>
+  <si>
+    <t>TEST 12</t>
   </si>
 </sst>
 </file>
@@ -414,7 +414,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>9991</v>
+        <v>9910</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -433,7 +433,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>9993</v>
+        <v>9912</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
